--- a/data/mapping.xlsx
+++ b/data/mapping.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clauses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mapping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contenu" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mapping" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,12 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,6 +453,16 @@
           <t>InsererApres</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,12 +472,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sustainable Finance Disclosure Clause</t>
+          <t>Sustainable Finance Disclosure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Risk Management:</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>apres_section</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>texte</t>
         </is>
       </c>
     </row>
@@ -476,12 +499,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stewardship Policy Clause</t>
+          <t>Stewardship Policy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Conflicts of interest</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>apres_section</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>liste</t>
         </is>
       </c>
     </row>
@@ -493,12 +526,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>German Investment Tax Act Clause</t>
+          <t>German Investment Tax Act</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Reference Currency:</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>apres_titre</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sous_titres</t>
         </is>
       </c>
     </row>
@@ -513,10 +556,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClauseID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Texte</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sous_texte</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CL01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The Management Company ensures compliance with Regulation (EU) 2019/2088 (SFDR). Pre-contractual and periodic disclosures are made available to investors in accordance with the applicable regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CL02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Monitor and engage with investee companies on ESG matters.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CL02</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Exercise voting rights in accordance with the Stewardship Policy.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CL02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Disclose engagement and voting outcomes in the annual report.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CL03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Equity fund status</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>At least 51% of the Compartment's assets consist of equity participations within the meaning of the German Investment Tax Act (InvStG).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CL03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mixed fund status</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>At least 25% of the Compartment's assets consist of equity participations within the meaning of the German Investment Tax Act (InvStG).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
